--- a/Result/profitability/9902.xlsx
+++ b/Result/profitability/9902.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02624999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>24.7875</v>
+        <v>17.54875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0825</v>
+        <v>0.03499999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.045</v>
+        <v>21.16375</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06999999999999999</v>
+        <v>0.03874999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>23.9775</v>
+        <v>24.49125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07500000000000001</v>
+        <v>0.02999999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>29.91125</v>
+        <v>30.7925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.001250000000000013</v>
       </c>
       <c r="N6" t="n">
-        <v>36.20625</v>
+        <v>34.30500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,13 +1266,13 @@
         <v>-0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1175</v>
+        <v>0.06249999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>35.00875000000001</v>
+        <v>36.80875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04625</v>
+        <v>0.03749999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>38.5125</v>
+        <v>36.69875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>-0.16</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08750000000000001</v>
+        <v>-0.08750000000000002</v>
       </c>
       <c r="N9" t="n">
         <v>30.6075</v>
@@ -1649,7 +1649,7 @@
         <v>1.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08749999999999998</v>
+        <v>0.08749999999999997</v>
       </c>
       <c r="N10" t="n">
         <v>30.53125</v>
@@ -9836,6 +9836,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9902</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20</v>
+      </c>
+      <c r="D75" t="n">
+        <v>17</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-36.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>90</v>
+      </c>
+      <c r="J75" t="n">
+        <v>82</v>
+      </c>
+      <c r="K75" t="n">
+        <v>82</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.941176470588235</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.51</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4571518588531821</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.050000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6925343811394893</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
